--- a/Key.xlsx
+++ b/Key.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\md\98KeyChk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7537D841-9BDF-40A2-8540-72D23F8EDDBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F1E4E3-A096-444C-81B2-01B15F4499CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14280" yWindow="2715" windowWidth="23460" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4350" yWindow="3345" windowWidth="23460" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,11 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="27">
-  <si>
-    <t>WIN・APP Mode</t>
-    <phoneticPr fontId="1"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="24">
   <si>
     <t>APP</t>
     <phoneticPr fontId="1"/>
@@ -63,18 +59,10 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Normal Mode</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>構成</t>
     <rPh sb="0" eb="2">
       <t>コウセイ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>98KeyChk.EXE</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -208,7 +196,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -233,8 +221,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="23"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -257,93 +251,51 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -626,40 +578,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="57.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="42.375" customWidth="1"/>
+    <col min="7" max="7" width="42.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2"/>
-      <c r="B3" s="19"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="13"/>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
@@ -670,217 +620,192 @@
         <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="13"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="56.25">
+      <c r="A7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="56.25">
+      <c r="A8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="8"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="8"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="B13" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="13"/>
+      <c r="B14" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="56.25">
-      <c r="A7" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="56.25">
-      <c r="A8" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="10"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" s="10"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="2"/>
-      <c r="B14" s="19"/>
       <c r="C14" s="1" t="s">
         <v>2</v>
       </c>
@@ -891,248 +816,225 @@
         <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="G14" s="13"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="F15" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="7" t="s">
+      <c r="G15" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="56.25">
+      <c r="A17" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="B17" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G17" s="9"/>
+    </row>
+    <row r="18" spans="1:7" ht="56.25">
+      <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="15" t="s">
+      <c r="B18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="56.25">
-      <c r="A17" s="8" t="s">
+      <c r="G18" s="10"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="11"/>
-    </row>
-    <row r="18" spans="1:8" ht="56.25">
-      <c r="A18" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="14"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="H19" s="10"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="H20" s="10"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
+      <c r="G20" s="8"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="6">
     <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B2:F2"/>
     <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="G2:G3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
